--- a/Unterschiede_K3V_Netzleitzahlen.xlsx
+++ b/Unterschiede_K3V_Netzleitzahlen.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,75 +541,75 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>498</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>499</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>501</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>542</v>
       </c>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="n">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="n">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="n">
-        <v>565</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="n">
+      <c r="A26" t="n">
+        <v>563</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>566</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="n">
         <v>567</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="n">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>702</v>
-      </c>
-      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>703</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>704</v>
       </c>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="n">
-        <v>745</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -630,110 +630,104 @@
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="n">
-        <v>838</v>
-      </c>
+      <c r="A35" t="n">
+        <v>839</v>
+      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="n">
-        <v>840</v>
-      </c>
+      <c r="A36" t="n">
+        <v>861</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>866</v>
+        <v>883</v>
       </c>
       <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>893</v>
+        <v>907</v>
       </c>
       <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>907</v>
-      </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>990</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="n">
         <v>992</v>
       </c>
     </row>
@@ -748,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,55 +856,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLA32 </t>
+          <t>SCHUH60</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLA32</t>
+          <t>SCHU60</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCHUH60</t>
+          <t>SCHUH59T</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SCHU60</t>
+          <t>SCHU59t</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCHUH59T</t>
+          <t>BAYR105E</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SCHU59t</t>
+          <t>BAYR105-EZ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAYR105E</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BAYR105-EZ</t>
-        </is>
-      </c>
+          <t>WÖM2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WÖM2</t>
+          <t>WÖM1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -918,7 +908,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WÖM1</t>
+          <t>SF53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -926,7 +916,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SF53</t>
+          <t>SF71</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -934,51 +924,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SF71</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>AWO33</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AW033</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCHBS11 </t>
+          <t>BAYR105M</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SCHBS11</t>
+          <t>BAYR105-MT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWO33</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AW033</t>
-        </is>
-      </c>
+          <t>WELL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BAYR105M</t>
+          <t>ZHU9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAYR105-MT</t>
+          <t>ZHU</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>UWMOZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -986,83 +976,79 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZHU9</t>
+          <t>RITZ5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZHU</t>
+          <t>RITZ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UWMOZ</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>LAMPB6T</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LAMPB8t</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RITZ5</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RITZ</t>
+          <t>ZEN27t</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">JKA13 </t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>JKA13</t>
-        </is>
-      </c>
+          <t>UWHAM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LAMPB6T</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LAMPB8t</t>
-        </is>
-      </c>
+          <t>UWHAM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NOE49</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZEN27t</t>
+          <t>NOE049</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">THY30 </t>
+          <t>HAGS32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>THY30</t>
+          <t>HAGS32t</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UWHAM</t>
+          <t>BSS19T</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1070,7 +1056,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UWHAM</t>
+          <t>JAMS16T</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1078,31 +1064,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NOE49</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NOE049</t>
-        </is>
-      </c>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HAGS32</t>
+          <t>ADA3T</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HAGS32t</t>
+          <t>ADA3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BSS19T</t>
+          <t>EINS4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1110,7 +1092,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JAMS16T</t>
+          <t>HSPW7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1118,7 +1100,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HSPW5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1126,19 +1108,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ADA3T</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ADA3</t>
-        </is>
-      </c>
+          <t>EINS2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEBA1</t>
+          <t>GSS2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1146,175 +1124,183 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GSS2</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>ELI12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AKLOZ18t</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ELI12</t>
+          <t>SOT3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AKLOZ18t</t>
+          <t>STO3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOT3</t>
+          <t>GOER3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>STO3</t>
+          <t>GOER3t</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOER3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>GOER3t</t>
-        </is>
-      </c>
+          <t>ALF1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ALF1</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>IDZ25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JAMS16t</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">APR20 </t>
+          <t>WEIN41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>APR20</t>
+          <t>ASS14t</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IDZ25</t>
+          <t>WEIN19U</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JAMS16t</t>
+          <t>WEIN19U_x000D_</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>MAXPL40t</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WEIN19V</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WEIN41</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>ASS14t</t>
-        </is>
-      </c>
+          <t>ASS14T</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KHS1 </t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KHS1</t>
+          <t>ELTS35t</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WEIN19U</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>WEIN19U_x000D_</t>
-        </is>
-      </c>
+          <t>UWK</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>WEIN19t</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BUED</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>WIDRL3t</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ADU25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WUE15T</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ELTS35t</t>
+          <t>WUE15</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>COB1</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>COB1t</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>UWK</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>HEG16T</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HEG16</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BUED</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>DA1T</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DA1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ADU25</t>
+          <t>WGS16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1322,99 +1308,75 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">EGW13 </t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>EGW13</t>
-        </is>
-      </c>
+          <t>AKLOZ18T</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">KRI27 </t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>KRI27</t>
-        </is>
-      </c>
+          <t>FVS42T</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WUE15T</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>WUE15</t>
-        </is>
-      </c>
+          <t>FRA95T</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COB1</t>
+          <t>WALW4T</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COB1t</t>
+          <t>WALWA4t</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>FRA98t</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BUNS74</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HEG16T</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>HEG16</t>
-        </is>
-      </c>
+          <t>BAYR105A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DA1T</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>DA1</t>
-        </is>
-      </c>
+          <t>BAYR105B</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMS8 </t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>KMS8</t>
-        </is>
-      </c>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>WGS16</t>
+          <t>UINF</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1422,7 +1384,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AKLOZ18T</t>
+          <t>UMHB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1430,31 +1392,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FVS42T</t>
+          <t>UET</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>WUE55t</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UZW</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>WALWA4t</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>UNMI</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BUNS74</t>
+          <t>UCHN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1462,7 +1424,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BAYR105A</t>
+          <t>UCHA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1470,7 +1432,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BAYR105B</t>
+          <t>UPA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1478,7 +1440,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>UME</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1486,7 +1448,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>UINF</t>
+          <t>SIEP11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1494,122 +1456,50 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>UMHB</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>HSPW1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HSPOW1</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>UET</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>SCHUC3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SIEP11</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>UZW</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>SIEP12T</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SIEP 12t</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>UNMI</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>WEIN19P</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>UCHN</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>UCHA</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>UPA</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>UME</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SIEP11</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>HSPW1</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>HSPOW1</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>SCHUC3</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>SIEP11</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>SIEP12T</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>SIEP 12t</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>WEIN19P</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
         <is>
           <t>PARK2P</t>
         </is>
@@ -1626,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1812,7 +1702,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sebastianstr. 001a</t>
+          <t>Einsteinstr. 004</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1820,7 +1710,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Günther-Scharowsky-Str. 002t</t>
+          <t>Hertha-Sponer-Weg 007</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1828,31 +1718,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Elise-Spaeth-Str. 012</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Am Klosterholz 018t</t>
-        </is>
-      </c>
+          <t>Hertha-Sponer-Weg 005</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cumianastr. 005a</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Cumianastr. 005t</t>
-        </is>
-      </c>
+          <t>Einsteinstr. 002</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alfred-Mehl-Str. 001b</t>
+          <t>Günther-Scharowsky-Str. 002t</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1860,103 +1742,115 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>In der Zeil 025b</t>
+          <t>Elise-Spaeth-Str. 012</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jaminstr. 016t</t>
+          <t>Am Klosterholz 018t</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cumianastr. 005a</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Max-Planck-Str. 040t</t>
+          <t>Cumianastr. 005t</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Alfred-Mehl-Str. 001b</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>In der Zeil 025b</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Jaminstr. 016t</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Weinstr. 041</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Anschützstr. 014t</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Weinstr. 019t</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Widerlichstr. 003t</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Weinstr. 019v</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Anschützstr. 014t</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>Eltersdorfer Str. 35t</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Frauenauracher Straße 098t (Schalthaus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Kastenweiher</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Büchenbacher Damm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>Frauenauracher Straße 098t</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Frauenauracher Straße 098t (Schalthaus)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Am Dummetsweiher 025</t>
+          <t>Kastenweiher</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Frauenauracher Str. 098t (Netzstation)</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Büchenbacher Damm</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Willi-Grasser-Str. 016a</t>
+          <t>Am Dummetsweiher 025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1964,39 +1858,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Am Klosterholz 018t</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>Frauenauracher Straße 098t</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Frauenauracher Str. 098t (Netzstation)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Willi-Grasser-Str. 016a</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Am Klosterholz 018t</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Faust-von-Stromberg-Str. 042t</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Würzburger Ring 055t</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Walberlaweg 4t</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bunsenstr. 074</t>
+          <t>Frauenauracher Straße 095t</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2004,15 +1902,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bayreuther Str. 105 - Abwasserfilter</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>Walberlaweg 004t</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Walberlaweg 4t</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bayreuther Str. 105 - Biologischer Teil</t>
+          <t>Bunsenstr. 074</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2020,7 +1922,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UNI WW</t>
+          <t>Bayreuther Str. 105 - Abwasserfilter</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2028,7 +1930,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UNI INF</t>
+          <t>Bayreuther Str. 105 - Biologischer Teil</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2036,7 +1938,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UNI MHB</t>
+          <t>UNI WW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2044,7 +1946,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UNI ET</t>
+          <t>UNI INF</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2052,7 +1954,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UNI ZW</t>
+          <t>UNI MHB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2060,7 +1962,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>UNI NMI</t>
+          <t>UNI ET</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2068,7 +1970,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>UNI CHN</t>
+          <t>UNI ZW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2076,7 +1978,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UNI CHA</t>
+          <t>UNI NMI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2084,7 +1986,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UNI PA</t>
+          <t>UNI CHN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2092,7 +1994,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>UNI Mikroelektronik</t>
+          <t>UNI CHA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2100,7 +2002,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Siemenspromenade 011 (M213)</t>
+          <t>UNI PA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2108,48 +2010,52 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Herta-Sponer-Weg 001 (M221)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Hertha-Sponer-Weg 001 (M221)</t>
-        </is>
-      </c>
+          <t>UNI Mikroelektronik</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Siemenspromenade 011 (M213)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Herta-Sponer-Weg 001 (M221)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hertha-Sponer-Weg 001 (M221)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Schuckertstr. 003 (M233)</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Siemenspromenade 011 (M213)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Weinstr. 019P (Provisorium 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Parkplatzstr. 002P (Provisorium 2)</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Hertha-Sponer-Weg 8T</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Alfred-Mehl-Str. 001b</t>
+          <t>Hertha-Sponer-Weg 008t (M5, Framatome)</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2063,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Am Dummetsweiher 025</t>
+          <t>Weinstr. 019P (Provisorium 1)</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2071,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bissingerstr. 019t</t>
+          <t>Parkplatzstr. 002P (Provisorium 2)</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2079,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Böhmlach (Liegenschaft)</t>
+          <t>Alfred-Mehl-Str. 001b</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2087,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Büchenbacher Damm</t>
+          <t>Am Dummetsweiher 025</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2095,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bunsenstr. 074</t>
+          <t>Bissingerstr. 019t</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2103,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Erlangen-Mitte (Pommernstr. 038)</t>
+          <t>Böhmlach (Liegenschaft)</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2111,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fuchsenwiese 003</t>
+          <t>Büchenbacher Damm</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2119,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gas- und Dampfturbine 2</t>
+          <t>Bunsenstr. 074</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2127,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Günther-Scharowsky-Str. 002t</t>
+          <t>Erlangen-Mitte (Pommernstr. 038)</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2135,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hammerbacherstr.</t>
+          <t>Fuchsenwiese 003</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2143,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Heizkraftwerk</t>
+          <t>Gas- und Dampfturbine 2</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2151,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kastenweiher</t>
+          <t>Günther-Scharowsky-Str. 002t</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2159,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Litzendorf / Hohenellern</t>
+          <t>Hammerbacherstr.</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2167,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mozartstr. 035</t>
+          <t>Heizkraftwerk</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2175,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saidelsteig 35t </t>
+          <t>Kastenweiher</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2183,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sperlingstr. (Liegenschaft)</t>
+          <t>Litzendorf / Hohenellern</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2191,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tennenlohe</t>
+          <t>Mozartstr. 035</t>
         </is>
       </c>
     </row>
@@ -2293,13 +2199,37 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Werker 001t</t>
+          <t xml:space="preserve">Saidelsteig 35t </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
+        <is>
+          <t>Sperlingstr. (Liegenschaft)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tennenlohe</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Werker 001t</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
         <is>
           <t>Willi-Grasser-Str. 016a</t>
         </is>
@@ -2316,7 +2246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2510,7 +2440,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Süd</t>
+          <t>Südost</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -2518,26 +2448,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Süd</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Westnetz</t>
-        </is>
-      </c>
+          <t>Südost</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Süd</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Südnetz</t>
-        </is>
-      </c>
+          <t>Südost</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2555,12 +2477,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Südostnetz</t>
+          <t>Westnetz</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Süd</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Südnetz</t>
@@ -2573,51 +2499,55 @@
           <t>Süd</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Süd</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Südostnetz</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Süd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Südnetz</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Süd</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Süd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>Südnetz</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Südnetz</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Südnetz</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Westnetz</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2625,7 +2555,11 @@
           <t>West</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Westnetz</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2636,12 +2570,12 @@
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Westnetz</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2657,7 +2591,11 @@
           <t>West</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Westnetz</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2668,25 +2606,25 @@
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Ostnetz</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Westnetz</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Süd</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2694,15 +2632,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Westnetz</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Süd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2710,7 +2652,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Südost</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2718,7 +2660,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Südost</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2790,7 +2732,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Süd</t>
+          <t>Südost</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2798,14 +2740,10 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Süd</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Südnetz</t>
-        </is>
-      </c>
+          <t>Südost</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2813,30 +2751,38 @@
           <t>Süd</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Süd</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Südnetz</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Süd</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Südnetz</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Nordnetz</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Süd</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Südnetz</t>
@@ -2847,7 +2793,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Westnetz</t>
+          <t>Südnetz</t>
         </is>
       </c>
     </row>
@@ -2855,13 +2801,17 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Südostnetz</t>
+          <t>Nordnetz</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Südnetz</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -2881,17 +2831,13 @@
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Nordnetz und Südnetz</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nordnetz</t>
+          <t>Westnetz</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2845,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nordnetz und Ostnetz</t>
+          <t>Südostnetz</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2853,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Südnetz und Südostnetz</t>
+          <t>Nordnetz und Südnetz</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2861,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Südostnetz</t>
+          <t>Nordnetz</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2869,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nordnetz</t>
+          <t>Nordnetz und Ostnetz</t>
         </is>
       </c>
     </row>
@@ -2931,25 +2877,33 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Westnetz</t>
+          <t>Südnetz und Südostnetz</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Südostnetz</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ostnetz</t>
+          <t>Nordnetz</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Westnetz</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -2959,21 +2913,37 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Südostnetz</t>
+          <t>Ostnetz</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Nordnetz</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Südostnetz</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Nordnetz</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
         <is>
           <t>Westnetz</t>
         </is>
